--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/8.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/8.xlsx
@@ -426,13 +426,13 @@
         <v>-1.649490260623037</v>
       </c>
       <c r="E2">
-        <v>-10.94069513783028</v>
+        <v>-7.462214524833382</v>
       </c>
       <c r="F2">
-        <v>-5.344091504767709</v>
+        <v>-5.777203401321431</v>
       </c>
       <c r="G2">
-        <v>-7.6528137232634</v>
+        <v>-1.139755252133402</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.263882039294144</v>
       </c>
       <c r="E3">
-        <v>-10.39608869001684</v>
+        <v>-8.394103775475759</v>
       </c>
       <c r="F3">
-        <v>-5.235480941117055</v>
+        <v>-6.053376123210369</v>
       </c>
       <c r="G3">
-        <v>-7.387551629827927</v>
+        <v>-1.213764639802282</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.857033951138093</v>
       </c>
       <c r="E4">
-        <v>-11.66155141463547</v>
+        <v>-8.307683754228728</v>
       </c>
       <c r="F4">
-        <v>-5.178722863412038</v>
+        <v>-6.275658575342783</v>
       </c>
       <c r="G4">
-        <v>-7.700198737592107</v>
+        <v>-1.396848325743283</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.33653164538617</v>
       </c>
       <c r="E5">
-        <v>-12.3469683392059</v>
+        <v>-8.859803361328785</v>
       </c>
       <c r="F5">
-        <v>-5.236154403815531</v>
+        <v>-6.181434268376548</v>
       </c>
       <c r="G5">
-        <v>-7.12085362686734</v>
+        <v>-1.604540890200118</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.696607363429445</v>
       </c>
       <c r="E6">
-        <v>-13.60607665049754</v>
+        <v>-9.302519075710208</v>
       </c>
       <c r="F6">
-        <v>-5.030184162579046</v>
+        <v>-6.031178361917551</v>
       </c>
       <c r="G6">
-        <v>-6.662380769221936</v>
+        <v>-2.135354869720681</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.916550814873879</v>
       </c>
       <c r="E7">
-        <v>-13.38990200104022</v>
+        <v>-10.69180148955595</v>
       </c>
       <c r="F7">
-        <v>-5.257081449512455</v>
+        <v>-6.09463047660459</v>
       </c>
       <c r="G7">
-        <v>-8.595693269950033</v>
+        <v>-2.036183125682651</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.995021864087321</v>
       </c>
       <c r="E8">
-        <v>-14.22685299400834</v>
+        <v>-10.87347956574925</v>
       </c>
       <c r="F8">
-        <v>-5.427606677950553</v>
+        <v>-6.023732995701189</v>
       </c>
       <c r="G8">
-        <v>-8.009166000855114</v>
+        <v>-2.4868576892344</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.936269097503495</v>
       </c>
       <c r="E9">
-        <v>-14.48475911085754</v>
+        <v>-10.83768719055188</v>
       </c>
       <c r="F9">
-        <v>-5.363805820586935</v>
+        <v>-5.881185876292644</v>
       </c>
       <c r="G9">
-        <v>-8.199080700018763</v>
+        <v>-2.592133354126452</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.755608382034673</v>
       </c>
       <c r="E10">
-        <v>-13.88917614724316</v>
+        <v>-11.87893049537699</v>
       </c>
       <c r="F10">
-        <v>-4.474386083466301</v>
+        <v>-5.772460169573001</v>
       </c>
       <c r="G10">
-        <v>-7.939542664099304</v>
+        <v>-2.561250856358173</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.477145055409188</v>
       </c>
       <c r="E11">
-        <v>-15.57432918265836</v>
+        <v>-12.37137260895059</v>
       </c>
       <c r="F11">
-        <v>-4.511761192313211</v>
+        <v>-5.756890175869981</v>
       </c>
       <c r="G11">
-        <v>-7.265154701907353</v>
+        <v>-2.519387566839672</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.137312755357072</v>
       </c>
       <c r="E12">
-        <v>-15.39216518074006</v>
+        <v>-13.16759721166745</v>
       </c>
       <c r="F12">
-        <v>-4.100857825828545</v>
+        <v>-5.675735849785116</v>
       </c>
       <c r="G12">
-        <v>-7.439414071130392</v>
+        <v>-2.110216010052851</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.773983808980739</v>
       </c>
       <c r="E13">
-        <v>-16.77476923077548</v>
+        <v>-13.3686375590571</v>
       </c>
       <c r="F13">
-        <v>-4.350638762264291</v>
+        <v>-5.206134369138077</v>
       </c>
       <c r="G13">
-        <v>-6.227065216099707</v>
+        <v>-2.130248253300463</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.435934269478726</v>
       </c>
       <c r="E14">
-        <v>-17.40674678522934</v>
+        <v>-15.07240113441886</v>
       </c>
       <c r="F14">
-        <v>-4.649842583053263</v>
+        <v>-5.151494426882019</v>
       </c>
       <c r="G14">
-        <v>-6.932018470592116</v>
+        <v>-1.794806734511273</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.160335733078075</v>
       </c>
       <c r="E15">
-        <v>-19.3708253400087</v>
+        <v>-15.47529585861782</v>
       </c>
       <c r="F15">
-        <v>-3.637334076815844</v>
+        <v>-4.507929164707861</v>
       </c>
       <c r="G15">
-        <v>-5.223202591881555</v>
+        <v>-1.57581747820869</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.982924180504187</v>
       </c>
       <c r="E16">
-        <v>-17.64527401803689</v>
+        <v>-17.03338554676123</v>
       </c>
       <c r="F16">
-        <v>-3.307407765791843</v>
+        <v>-4.164377866642613</v>
       </c>
       <c r="G16">
-        <v>-6.177275706002585</v>
+        <v>-1.201995403185543</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.926389469171068</v>
       </c>
       <c r="E17">
-        <v>-19.53552093509478</v>
+        <v>-16.89066459279482</v>
       </c>
       <c r="F17">
-        <v>-3.509814370461486</v>
+        <v>-4.089750247324406</v>
       </c>
       <c r="G17">
-        <v>-5.865464036507561</v>
+        <v>-0.9611046105081114</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.99442821305245</v>
       </c>
       <c r="E18">
-        <v>-20.91362290405409</v>
+        <v>-18.57249505915016</v>
       </c>
       <c r="F18">
-        <v>-3.327634012665999</v>
+        <v>-3.433037966100416</v>
       </c>
       <c r="G18">
-        <v>-6.28837333133282</v>
+        <v>-0.7811694825439927</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.188535253770449</v>
       </c>
       <c r="E19">
-        <v>-22.21656420766797</v>
+        <v>-19.42804828564219</v>
       </c>
       <c r="F19">
-        <v>-2.55778828177207</v>
+        <v>-3.128050484105097</v>
       </c>
       <c r="G19">
-        <v>-4.711817773608058</v>
+        <v>-0.3948445516740042</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.485587685952979</v>
       </c>
       <c r="E20">
-        <v>-21.40916746648733</v>
+        <v>-19.78061854821821</v>
       </c>
       <c r="F20">
-        <v>-2.518577510760555</v>
+        <v>-2.819659240451675</v>
       </c>
       <c r="G20">
-        <v>-5.221905051819771</v>
+        <v>-0.4842651646642253</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.865598167174964</v>
       </c>
       <c r="E21">
-        <v>-24.11926660548902</v>
+        <v>-21.72815070907946</v>
       </c>
       <c r="F21">
-        <v>-2.093311910246151</v>
+        <v>-2.522285283255486</v>
       </c>
       <c r="G21">
-        <v>-4.792557660832827</v>
+        <v>-0.1535438720957676</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.298403958757478</v>
       </c>
       <c r="E22">
-        <v>-23.54449953703468</v>
+        <v>-22.0573051662061</v>
       </c>
       <c r="F22">
-        <v>-2.098174426900584</v>
+        <v>-2.097677406458904</v>
       </c>
       <c r="G22">
-        <v>-4.147547102152379</v>
+        <v>-0.3509997070108477</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.749133460407278</v>
       </c>
       <c r="E23">
-        <v>-24.87207769022745</v>
+        <v>-21.86445910476034</v>
       </c>
       <c r="F23">
-        <v>-1.009119802440074</v>
+        <v>-1.870939166066832</v>
       </c>
       <c r="G23">
-        <v>-4.646744964674559</v>
+        <v>-0.5394145334069024</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.192308972004366</v>
       </c>
       <c r="E24">
-        <v>-25.15840007896113</v>
+        <v>-22.93744125052979</v>
       </c>
       <c r="F24">
-        <v>-1.329612665480994</v>
+        <v>-1.534644366450108</v>
       </c>
       <c r="G24">
-        <v>-4.751485426925433</v>
+        <v>-0.4751432230628755</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.595180443789365</v>
       </c>
       <c r="E25">
-        <v>-25.13692797641176</v>
+        <v>-23.42837990160379</v>
       </c>
       <c r="F25">
-        <v>-0.6843186005371933</v>
+        <v>-1.60964309436477</v>
       </c>
       <c r="G25">
-        <v>-4.915769141065828</v>
+        <v>-0.5479908293887096</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.940152366771458</v>
       </c>
       <c r="E26">
-        <v>-26.01620434599121</v>
+        <v>-23.00037486173492</v>
       </c>
       <c r="F26">
-        <v>-0.9446305717647295</v>
+        <v>-1.570184641499818</v>
       </c>
       <c r="G26">
-        <v>-4.628775209653926</v>
+        <v>-0.640069180372684</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.209389824406164</v>
       </c>
       <c r="E27">
-        <v>-24.29721509791263</v>
+        <v>-23.29175586186224</v>
       </c>
       <c r="F27">
-        <v>-0.4856760973458719</v>
+        <v>-1.343405811105009</v>
       </c>
       <c r="G27">
-        <v>-5.461775043362078</v>
+        <v>-0.471858906367255</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.390097771613129</v>
       </c>
       <c r="E28">
-        <v>-26.1310198730661</v>
+        <v>-22.91010481358977</v>
       </c>
       <c r="F28">
-        <v>-1.062490685835043</v>
+        <v>-1.29170408802668</v>
       </c>
       <c r="G28">
-        <v>-4.579586170812761</v>
+        <v>-1.0970695780687</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.478464851609934</v>
       </c>
       <c r="E29">
-        <v>-25.03698509909109</v>
+        <v>-24.69670418882523</v>
       </c>
       <c r="F29">
-        <v>-0.4664737125815765</v>
+        <v>-1.68805303924416</v>
       </c>
       <c r="G29">
-        <v>-5.108815428366517</v>
+        <v>-1.398378222073676</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.468898159028408</v>
       </c>
       <c r="E30">
-        <v>-26.25109336567822</v>
+        <v>-23.14192876331905</v>
       </c>
       <c r="F30">
-        <v>-1.305627287332934</v>
+        <v>-1.845137178204433</v>
       </c>
       <c r="G30">
-        <v>-4.973571026313076</v>
+        <v>-0.82869808782521</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.367219893070653</v>
       </c>
       <c r="E31">
-        <v>-23.87775736695025</v>
+        <v>-22.81438990539777</v>
       </c>
       <c r="F31">
-        <v>-0.6765534845033507</v>
+        <v>-1.801473104035468</v>
       </c>
       <c r="G31">
-        <v>-3.975668731996436</v>
+        <v>-0.7015130543245351</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.179073285627591</v>
       </c>
       <c r="E32">
-        <v>-25.59950019413719</v>
+        <v>-22.7779288631771</v>
       </c>
       <c r="F32">
-        <v>-1.214603792011116</v>
+        <v>-2.029807608412735</v>
       </c>
       <c r="G32">
-        <v>-4.862269762904734</v>
+        <v>-0.7358339027193105</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.914088646227035</v>
       </c>
       <c r="E33">
-        <v>-24.71933919054555</v>
+        <v>-22.15507176079256</v>
       </c>
       <c r="F33">
-        <v>-2.16030281047795</v>
+        <v>-2.09496864505175</v>
       </c>
       <c r="G33">
-        <v>-3.879608995511013</v>
+        <v>-0.6193607542759734</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.585815485512205</v>
       </c>
       <c r="E34">
-        <v>-24.63524496764042</v>
+        <v>-21.57522946809927</v>
       </c>
       <c r="F34">
-        <v>-0.8963152146290456</v>
+        <v>-2.174230979988621</v>
       </c>
       <c r="G34">
-        <v>-3.774074866904441</v>
+        <v>-0.04576972463002009</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.202542426973327</v>
       </c>
       <c r="E35">
-        <v>-23.91008596390271</v>
+        <v>-22.30735756044005</v>
       </c>
       <c r="F35">
-        <v>-1.494878589278718</v>
+        <v>-2.27656417546086</v>
       </c>
       <c r="G35">
-        <v>-3.351938352478152</v>
+        <v>0.001307221836934679</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.779424106416965</v>
       </c>
       <c r="E36">
-        <v>-23.79661607729707</v>
+        <v>-21.49979469080641</v>
       </c>
       <c r="F36">
-        <v>-1.32015436647583</v>
+        <v>-2.167401090752539</v>
       </c>
       <c r="G36">
-        <v>-3.747656742386966</v>
+        <v>0.5297871956930416</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.326112648389229</v>
       </c>
       <c r="E37">
-        <v>-23.13814518780213</v>
+        <v>-20.24774683876698</v>
       </c>
       <c r="F37">
-        <v>-1.202662047532359</v>
+        <v>-2.243219074028569</v>
       </c>
       <c r="G37">
-        <v>-3.39259808874015</v>
+        <v>0.6352456127064716</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.855366568052405</v>
       </c>
       <c r="E38">
-        <v>-22.43794698412663</v>
+        <v>-20.64852342519028</v>
       </c>
       <c r="F38">
-        <v>-1.764102965392974</v>
+        <v>-2.147884754742582</v>
       </c>
       <c r="G38">
-        <v>-2.378075794356483</v>
+        <v>0.977991994861597</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.383710229731113</v>
       </c>
       <c r="E39">
-        <v>-22.82633454116797</v>
+        <v>-20.24012569598592</v>
       </c>
       <c r="F39">
-        <v>-1.764455021539164</v>
+        <v>-2.286498785722635</v>
       </c>
       <c r="G39">
-        <v>-2.397222995187708</v>
+        <v>1.475876652854447</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.922826817329308</v>
       </c>
       <c r="E40">
-        <v>-23.03479667719509</v>
+        <v>-20.04215872497664</v>
       </c>
       <c r="F40">
-        <v>-1.41837471779317</v>
+        <v>-1.951234475154994</v>
       </c>
       <c r="G40">
-        <v>-2.788022742286864</v>
+        <v>2.127750859064933</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.495320369759904</v>
       </c>
       <c r="E41">
-        <v>-19.55487905307981</v>
+        <v>-19.46584666190946</v>
       </c>
       <c r="F41">
-        <v>-1.199216039136713</v>
+        <v>-2.03092756114132</v>
       </c>
       <c r="G41">
-        <v>-1.840251965608781</v>
+        <v>2.101677352833484</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.115459469721289</v>
       </c>
       <c r="E42">
-        <v>-22.23089278673863</v>
+        <v>-19.36682164429157</v>
       </c>
       <c r="F42">
-        <v>-1.335724360178849</v>
+        <v>-2.105760615575422</v>
       </c>
       <c r="G42">
-        <v>-1.728958534434213</v>
+        <v>2.33333916338133</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.8010170925077462</v>
       </c>
       <c r="E43">
-        <v>-19.65644583602849</v>
+        <v>-19.05420112144908</v>
       </c>
       <c r="F43">
-        <v>-1.278523105913335</v>
+        <v>-2.177121153856988</v>
       </c>
       <c r="G43">
-        <v>-2.426076944408692</v>
+        <v>2.496557693728551</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.5683157208606536</v>
       </c>
       <c r="E44">
-        <v>-20.0684983911987</v>
+        <v>-18.43744508650071</v>
       </c>
       <c r="F44">
-        <v>-0.8616571508633171</v>
+        <v>-1.822422515652268</v>
       </c>
       <c r="G44">
-        <v>-1.164345855437098</v>
+        <v>2.751979890800119</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.4235876287475042</v>
       </c>
       <c r="E45">
-        <v>-19.77935597197547</v>
+        <v>-18.01791259773448</v>
       </c>
       <c r="F45">
-        <v>-1.635914766544556</v>
+        <v>-2.226490194329033</v>
       </c>
       <c r="G45">
-        <v>-1.53149486728536</v>
+        <v>3.071036376535483</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.3805044606373171</v>
       </c>
       <c r="E46">
-        <v>-20.12295114487853</v>
+        <v>-17.90849624538188</v>
       </c>
       <c r="F46">
-        <v>-1.594367999457147</v>
+        <v>-1.98414302696601</v>
       </c>
       <c r="G46">
-        <v>-1.298310992640894</v>
+        <v>3.179113370373799</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.4374224508398232</v>
       </c>
       <c r="E47">
-        <v>-21.19900251381703</v>
+        <v>-17.22571245679139</v>
       </c>
       <c r="F47">
-        <v>-1.834153026443311</v>
+        <v>-1.95637615162417</v>
       </c>
       <c r="G47">
-        <v>-1.025733592861121</v>
+        <v>3.498203795788847</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.5945215785733099</v>
       </c>
       <c r="E48">
-        <v>-17.93052903146009</v>
+        <v>-17.4524736419157</v>
       </c>
       <c r="F48">
-        <v>-1.199137344233447</v>
+        <v>-2.506422047491875</v>
       </c>
       <c r="G48">
-        <v>-1.612521936415152</v>
+        <v>4.068868180748162</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.8450989781203991</v>
       </c>
       <c r="E49">
-        <v>-18.2355242583102</v>
+        <v>-17.05221205369667</v>
       </c>
       <c r="F49">
-        <v>-1.427714560259734</v>
+        <v>-2.019106758303371</v>
       </c>
       <c r="G49">
-        <v>-1.293154772073446</v>
+        <v>3.405394436319361</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.172229514019365</v>
       </c>
       <c r="E50">
-        <v>-16.76674107328459</v>
+        <v>-15.83597318969991</v>
       </c>
       <c r="F50">
-        <v>-1.935145095090419</v>
+        <v>-2.362388008595306</v>
       </c>
       <c r="G50">
-        <v>-0.8377965327252398</v>
+        <v>3.133592427683148</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.563525705155353</v>
       </c>
       <c r="E51">
-        <v>-17.50839663240452</v>
+        <v>-16.08795267398858</v>
       </c>
       <c r="F51">
-        <v>-1.637006554781446</v>
+        <v>-2.460639837873952</v>
       </c>
       <c r="G51">
-        <v>-1.130667250211737</v>
+        <v>3.677721204618388</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.994359503438901</v>
       </c>
       <c r="E52">
-        <v>-17.89111920919879</v>
+        <v>-15.74905893630522</v>
       </c>
       <c r="F52">
-        <v>-0.8530437866090078</v>
+        <v>-2.217974577428254</v>
       </c>
       <c r="G52">
-        <v>-1.380935837460448</v>
+        <v>3.364168168481091</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.44670996525514</v>
       </c>
       <c r="E53">
-        <v>-17.09767725806957</v>
+        <v>-14.20482851435277</v>
       </c>
       <c r="F53">
-        <v>-1.451578996766985</v>
+        <v>-2.279779069351125</v>
       </c>
       <c r="G53">
-        <v>-1.037137325235104</v>
+        <v>3.137780062007294</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.900157833854009</v>
       </c>
       <c r="E54">
-        <v>-17.38551141572549</v>
+        <v>-14.09186116631744</v>
       </c>
       <c r="F54">
-        <v>-1.119038358219749</v>
+        <v>-2.382796496298077</v>
       </c>
       <c r="G54">
-        <v>-1.321389974826336</v>
+        <v>2.858892492550799</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.333307200871559</v>
       </c>
       <c r="E55">
-        <v>-15.81559338172898</v>
+        <v>-14.40639216636935</v>
       </c>
       <c r="F55">
-        <v>-1.666682816986738</v>
+        <v>-2.371771754534219</v>
       </c>
       <c r="G55">
-        <v>-1.095268164300832</v>
+        <v>2.475413273285124</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.732754243649012</v>
       </c>
       <c r="E56">
-        <v>-15.93716618362936</v>
+        <v>-13.79578703739306</v>
       </c>
       <c r="F56">
-        <v>-1.978269902080161</v>
+        <v>-2.36347234152557</v>
       </c>
       <c r="G56">
-        <v>-1.497970295990874</v>
+        <v>2.946926800163139</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.080494825170827</v>
       </c>
       <c r="E57">
-        <v>-16.53074729938518</v>
+        <v>-13.81453878652466</v>
       </c>
       <c r="F57">
-        <v>-1.242055059372489</v>
+        <v>-2.321911492192314</v>
       </c>
       <c r="G57">
-        <v>-1.606600767682507</v>
+        <v>2.413327156163859</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.36991961766412</v>
       </c>
       <c r="E58">
-        <v>-16.45487643490321</v>
+        <v>-13.93927218224324</v>
       </c>
       <c r="F58">
-        <v>-1.704500274026744</v>
+        <v>-2.067972979761917</v>
       </c>
       <c r="G58">
-        <v>-1.981514133944739</v>
+        <v>2.603102180491884</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.594996161976002</v>
       </c>
       <c r="E59">
-        <v>-15.55092168363163</v>
+        <v>-12.44000442609338</v>
       </c>
       <c r="F59">
-        <v>-1.443025274965677</v>
+        <v>-2.306736629740429</v>
       </c>
       <c r="G59">
-        <v>-1.902173605820806</v>
+        <v>2.47125174640689</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.75363689427925</v>
       </c>
       <c r="E60">
-        <v>-15.08892676228035</v>
+        <v>-12.61345083744087</v>
       </c>
       <c r="F60">
-        <v>-1.763155313084172</v>
+        <v>-2.102826538234706</v>
       </c>
       <c r="G60">
-        <v>-1.588197629059749</v>
+        <v>2.608655234237182</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.853347953381776</v>
       </c>
       <c r="E61">
-        <v>-14.56214589747307</v>
+        <v>-12.86106529662715</v>
       </c>
       <c r="F61">
-        <v>-2.12896732836485</v>
+        <v>-2.523557655586186</v>
       </c>
       <c r="G61">
-        <v>-2.496183268913857</v>
+        <v>2.543890493165435</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.897126066839683</v>
       </c>
       <c r="E62">
-        <v>-14.05933736843271</v>
+        <v>-12.22466041890102</v>
       </c>
       <c r="F62">
-        <v>-1.773884327685231</v>
+        <v>-2.4658618659812</v>
       </c>
       <c r="G62">
-        <v>-2.503354984305645</v>
+        <v>2.243041340208495</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.899088479172536</v>
       </c>
       <c r="E63">
-        <v>-12.86975796793002</v>
+        <v>-11.88170484054198</v>
       </c>
       <c r="F63">
-        <v>-1.71821969495191</v>
+        <v>-2.354189656409799</v>
       </c>
       <c r="G63">
-        <v>-2.72582175240359</v>
+        <v>1.327784776668137</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.868191239633515</v>
       </c>
       <c r="E64">
-        <v>-13.22320040488425</v>
+        <v>-12.13476000656378</v>
       </c>
       <c r="F64">
-        <v>-1.906418141928735</v>
+        <v>-2.530171340930137</v>
       </c>
       <c r="G64">
-        <v>-3.413259521434221</v>
+        <v>1.675047746965889</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.813880476147657</v>
       </c>
       <c r="E65">
-        <v>-13.58985836027409</v>
+        <v>-11.31036832464194</v>
       </c>
       <c r="F65">
-        <v>-2.052249738089379</v>
+        <v>-2.422614460615844</v>
       </c>
       <c r="G65">
-        <v>-3.003424835521257</v>
+        <v>1.30513656734023</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.748955165691067</v>
       </c>
       <c r="E66">
-        <v>-14.17698953884245</v>
+        <v>-11.50622961750953</v>
       </c>
       <c r="F66">
-        <v>-1.847730796542598</v>
+        <v>-2.412569677489497</v>
       </c>
       <c r="G66">
-        <v>-3.636013471437189</v>
+        <v>1.585167642927632</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.675040036299063</v>
       </c>
       <c r="E67">
-        <v>-12.67472316411607</v>
+        <v>-11.46800346047581</v>
       </c>
       <c r="F67">
-        <v>-2.205739590888905</v>
+        <v>-2.684252648055262</v>
       </c>
       <c r="G67">
-        <v>-2.656960753068386</v>
+        <v>1.117927904945269</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.601647789383404</v>
       </c>
       <c r="E68">
-        <v>-12.95777282232578</v>
+        <v>-11.33296179424901</v>
       </c>
       <c r="F68">
-        <v>-1.701994462633275</v>
+        <v>-2.676227424656941</v>
       </c>
       <c r="G68">
-        <v>-3.476476090963438</v>
+        <v>1.138281269777588</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.527162873570144</v>
       </c>
       <c r="E69">
-        <v>-13.01968889675633</v>
+        <v>-10.43079707705843</v>
       </c>
       <c r="F69">
-        <v>-2.482853338147424</v>
+        <v>-2.869808603017157</v>
       </c>
       <c r="G69">
-        <v>-3.915989721388177</v>
+        <v>1.194412278486524</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.449821439149297</v>
       </c>
       <c r="E70">
-        <v>-13.04341619305507</v>
+        <v>-10.70510007221806</v>
       </c>
       <c r="F70">
-        <v>-2.201951466755903</v>
+        <v>-2.877968850302135</v>
       </c>
       <c r="G70">
-        <v>-4.187238252171074</v>
+        <v>0.9528505244491762</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.368811750934947</v>
       </c>
       <c r="E71">
-        <v>-12.34474637114712</v>
+        <v>-11.31396915886057</v>
       </c>
       <c r="F71">
-        <v>-2.378158467209803</v>
+        <v>-3.112795270015142</v>
       </c>
       <c r="G71">
-        <v>-3.83964110656566</v>
+        <v>1.071809101743253</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.273239738716758</v>
       </c>
       <c r="E72">
-        <v>-12.22782516593054</v>
+        <v>-10.16118721069586</v>
       </c>
       <c r="F72">
-        <v>-1.828506045858427</v>
+        <v>-2.941319904166033</v>
       </c>
       <c r="G72">
-        <v>-3.749100484145851</v>
+        <v>1.382349338622405</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.161183777302968</v>
       </c>
       <c r="E73">
-        <v>-12.0799459234987</v>
+        <v>-10.7052080557125</v>
       </c>
       <c r="F73">
-        <v>-2.705033901089293</v>
+        <v>-3.109518248569667</v>
       </c>
       <c r="G73">
-        <v>-2.782433138117291</v>
+        <v>0.8955446806742395</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.022054514371653</v>
       </c>
       <c r="E74">
-        <v>-12.86928865505031</v>
+        <v>-10.94030473596574</v>
       </c>
       <c r="F74">
-        <v>-2.482985048564469</v>
+        <v>-3.178190734629148</v>
       </c>
       <c r="G74">
-        <v>-3.800211031006076</v>
+        <v>1.209930544336101</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.851953155521841</v>
       </c>
       <c r="E75">
-        <v>-12.44349312360624</v>
+        <v>-11.70623166206797</v>
       </c>
       <c r="F75">
-        <v>-2.703435980369293</v>
+        <v>-3.621469184317428</v>
       </c>
       <c r="G75">
-        <v>-3.088221819840617</v>
+        <v>0.840729487239225</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.65178827204931</v>
       </c>
       <c r="E76">
-        <v>-12.21903281755588</v>
+        <v>-11.24524181785731</v>
       </c>
       <c r="F76">
-        <v>-3.547428049120403</v>
+        <v>-3.393008768094936</v>
       </c>
       <c r="G76">
-        <v>-4.142928694970699</v>
+        <v>0.6895438787124457</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.419464821462368</v>
       </c>
       <c r="E77">
-        <v>-12.58794181348378</v>
+        <v>-11.34660094023975</v>
       </c>
       <c r="F77">
-        <v>-2.699993285443258</v>
+        <v>-3.473991622127421</v>
       </c>
       <c r="G77">
-        <v>-3.7408896924068</v>
+        <v>1.308812495724517</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.165055729798659</v>
       </c>
       <c r="E78">
-        <v>-14.10392624521607</v>
+        <v>-11.36981739154554</v>
       </c>
       <c r="F78">
-        <v>-2.95429710789829</v>
+        <v>-4.012599420897271</v>
       </c>
       <c r="G78">
-        <v>-3.562494903751438</v>
+        <v>1.542492411841294</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.892548929759854</v>
       </c>
       <c r="E79">
-        <v>-13.84681754494123</v>
+        <v>-11.68759620285347</v>
       </c>
       <c r="F79">
-        <v>-3.420404534840321</v>
+        <v>-3.576214644735089</v>
       </c>
       <c r="G79">
-        <v>-2.965882328301048</v>
+        <v>1.296622929228609</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.611985342389189</v>
       </c>
       <c r="E80">
-        <v>-14.69729970040564</v>
+        <v>-11.58538982536076</v>
       </c>
       <c r="F80">
-        <v>-3.321316054484847</v>
+        <v>-4.026173877526946</v>
       </c>
       <c r="G80">
-        <v>-2.20687882853882</v>
+        <v>0.6834504008367873</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.333625677599821</v>
       </c>
       <c r="E81">
-        <v>-14.2120260295787</v>
+        <v>-12.70937340619911</v>
       </c>
       <c r="F81">
-        <v>-3.594077559409057</v>
+        <v>-3.922097797039216</v>
       </c>
       <c r="G81">
-        <v>-2.49961378730658</v>
+        <v>1.11579492661433</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.063128477939464</v>
       </c>
       <c r="E82">
-        <v>-15.63148152369933</v>
+        <v>-13.15988885144856</v>
       </c>
       <c r="F82">
-        <v>-3.349375343519875</v>
+        <v>-4.326020511420491</v>
       </c>
       <c r="G82">
-        <v>-2.965602978629799</v>
+        <v>1.343206444967844</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.814925031837995</v>
       </c>
       <c r="E83">
-        <v>-16.64251852255896</v>
+        <v>-13.57720352536733</v>
       </c>
       <c r="F83">
-        <v>-3.699496423456725</v>
+        <v>-4.375336536378757</v>
       </c>
       <c r="G83">
-        <v>-2.736768604474128</v>
+        <v>1.401204136059425</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.594122705841629</v>
       </c>
       <c r="E84">
-        <v>-16.51790972318013</v>
+        <v>-14.74691396289204</v>
       </c>
       <c r="F84">
-        <v>-3.921440073321394</v>
+        <v>-4.392352859567065</v>
       </c>
       <c r="G84">
-        <v>-3.085112423032601</v>
+        <v>0.9642307601218389</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.412353954578288</v>
       </c>
       <c r="E85">
-        <v>-15.98271860544008</v>
+        <v>-15.612106792869</v>
       </c>
       <c r="F85">
-        <v>-3.891473054157719</v>
+        <v>-4.632328411055873</v>
       </c>
       <c r="G85">
-        <v>-2.96762369494332</v>
+        <v>1.476918339946302</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.278892776376221</v>
       </c>
       <c r="E86">
-        <v>-18.28250538481666</v>
+        <v>-16.2868624239686</v>
       </c>
       <c r="F86">
-        <v>-4.314755543109821</v>
+        <v>-4.59550002469481</v>
       </c>
       <c r="G86">
-        <v>-2.230239771140102</v>
+        <v>0.9795845490621762</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.198776015342509</v>
       </c>
       <c r="E87">
-        <v>-20.01377152557144</v>
+        <v>-17.35667151628588</v>
       </c>
       <c r="F87">
-        <v>-4.26691732559815</v>
+        <v>-5.031302458572824</v>
       </c>
       <c r="G87">
-        <v>-2.699288755124106</v>
+        <v>1.232544813984325</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.185512958640801</v>
       </c>
       <c r="E88">
-        <v>-22.04585060937222</v>
+        <v>-18.24483160488914</v>
       </c>
       <c r="F88">
-        <v>-4.418256736620008</v>
+        <v>-5.209529847122152</v>
       </c>
       <c r="G88">
-        <v>-2.681454758822211</v>
+        <v>0.8872555665974549</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.240094237323485</v>
       </c>
       <c r="E89">
-        <v>-21.47295663922537</v>
+        <v>-19.88566156904578</v>
       </c>
       <c r="F89">
-        <v>-4.397056329680161</v>
+        <v>-5.255096681215347</v>
       </c>
       <c r="G89">
-        <v>-1.727525235653692</v>
+        <v>0.7689131250268807</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.37336521834533</v>
       </c>
       <c r="E90">
-        <v>-24.50554848438868</v>
+        <v>-21.80808756744844</v>
       </c>
       <c r="F90">
-        <v>-4.128092060930384</v>
+        <v>-5.461236737769407</v>
       </c>
       <c r="G90">
-        <v>-2.613222948933466</v>
+        <v>0.7243868760254436</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.58955705120194</v>
       </c>
       <c r="E91">
-        <v>-25.32575788250642</v>
+        <v>-23.46848331015634</v>
       </c>
       <c r="F91">
-        <v>-4.165219487923857</v>
+        <v>-5.893442400384466</v>
       </c>
       <c r="G91">
-        <v>-2.27913118509788</v>
+        <v>0.5994966870203574</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.888354923795643</v>
       </c>
       <c r="E92">
-        <v>-27.17118749615808</v>
+        <v>-25.43333436224212</v>
       </c>
       <c r="F92">
-        <v>-4.604375153048404</v>
+        <v>-5.874721297081197</v>
       </c>
       <c r="G92">
-        <v>-2.57862014012285</v>
+        <v>0.420261238606657</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.276511775543646</v>
       </c>
       <c r="E93">
-        <v>-29.5431176328526</v>
+        <v>-27.17103798055039</v>
       </c>
       <c r="F93">
-        <v>-4.981867148708556</v>
+        <v>-6.06636906592328</v>
       </c>
       <c r="G93">
-        <v>-2.836937652945963</v>
+        <v>0.07611810809528588</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.742720958703605</v>
       </c>
       <c r="E94">
-        <v>-31.30703424443751</v>
+        <v>-29.595500010687</v>
       </c>
       <c r="F94">
-        <v>-4.982040277495741</v>
+        <v>-6.203302339443052</v>
       </c>
       <c r="G94">
-        <v>-2.30769273092466</v>
+        <v>0.08266063404061577</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.286065357309168</v>
       </c>
       <c r="E95">
-        <v>-33.13558105405375</v>
+        <v>-31.66276925404305</v>
       </c>
       <c r="F95">
-        <v>-5.080299562081013</v>
+        <v>-6.552319205631971</v>
       </c>
       <c r="G95">
-        <v>-3.786047741599287</v>
+        <v>-0.6678240061208094</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.899436069475553</v>
       </c>
       <c r="E96">
-        <v>-36.08547830852839</v>
+        <v>-33.34549058422757</v>
       </c>
       <c r="F96">
-        <v>-5.646168932076994</v>
+        <v>-6.814352524322524</v>
       </c>
       <c r="G96">
-        <v>-2.978353855212796</v>
+        <v>-0.7990530829931186</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.561750892311534</v>
       </c>
       <c r="E97">
-        <v>-38.37604080555253</v>
+        <v>-37.45298958860939</v>
       </c>
       <c r="F97">
-        <v>-5.725693031113149</v>
+        <v>-7.056309530638829</v>
       </c>
       <c r="G97">
-        <v>-3.213764694993481</v>
+        <v>-1.095808588431193</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.278285699646604</v>
       </c>
       <c r="E98">
-        <v>-40.65502414940305</v>
+        <v>-38.88348431843141</v>
       </c>
       <c r="F98">
-        <v>-5.937378179061549</v>
+        <v>-7.01473625579453</v>
       </c>
       <c r="G98">
-        <v>-3.597766063177379</v>
+        <v>-1.184568683039862</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.005158985312171</v>
       </c>
       <c r="E99">
-        <v>-44.88406065338899</v>
+        <v>-41.35943163275626</v>
       </c>
       <c r="F99">
-        <v>-5.789173310291884</v>
+        <v>-7.38276208295919</v>
       </c>
       <c r="G99">
-        <v>-4.427257056155074</v>
+        <v>-1.43436211477299</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.76640954573714</v>
       </c>
       <c r="E100">
-        <v>-46.10829444918604</v>
+        <v>-43.57809581193062</v>
       </c>
       <c r="F100">
-        <v>-5.794831888020408</v>
+        <v>-7.399941594525849</v>
       </c>
       <c r="G100">
-        <v>-4.591206594987806</v>
+        <v>-2.178669733231841</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.489137945851658</v>
       </c>
       <c r="E101">
-        <v>-48.83807254174761</v>
+        <v>-47.02322925289764</v>
       </c>
       <c r="F101">
-        <v>-5.408589019117082</v>
+        <v>-7.285020113816967</v>
       </c>
       <c r="G101">
-        <v>-4.794155436522589</v>
+        <v>-2.860614495642769</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.243659964831135</v>
       </c>
       <c r="E102">
-        <v>-51.47218348804741</v>
+        <v>-49.31508547524946</v>
       </c>
       <c r="F102">
-        <v>-6.045876913112825</v>
+        <v>-7.515664934880641</v>
       </c>
       <c r="G102">
-        <v>-5.807260096593281</v>
+        <v>-2.578842053413094</v>
       </c>
     </row>
   </sheetData>
